--- a/field_linkage_matrix.xlsx
+++ b/field_linkage_matrix.xlsx
@@ -10,11 +10,17 @@
     <sheet name="Field Rules" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Cross-Phase Flow" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Findings (visibility)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="REV1 - System Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="REV1 - Circuit Designer" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Gaps vs REV1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Field Rules'!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Cross-Phase Flow'!$A$1:$C$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Findings (visibility)'!$A$1:$C$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'REV1 - System Info'!$A$1:$O$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'REV1 - Circuit Designer'!$A$1:$AA$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Gaps vs REV1'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -23,7 +29,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,8 +41,19 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00188038"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00B52A29"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -46,6 +63,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001A73E8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F0FE"/>
       </patternFill>
     </fill>
   </fills>
@@ -75,12 +97,27 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -11196,4 +11233,8389 @@
   <autoFilter ref="A1:C1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:O60"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="10" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="22" customWidth="1" min="12" max="12"/>
+    <col width="8" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="34" customWidth="1" min="15" max="15"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Display Name</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Base User/Ref</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>Combo list</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Default</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2 applies</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2 disp/UR</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>HFC applies</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>HFC disp/UR</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2 applies</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2 disp/UR</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol applies</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol disp/UR</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>Impl status (auto)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>system_designation</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>System Designation</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E2" s="4" t="inlineStr"/>
+      <c r="F2" s="4" t="inlineStr"/>
+      <c r="G2" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H2" s="4" t="inlineStr"/>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J2" s="4" t="inlineStr"/>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L2" s="4" t="inlineStr"/>
+      <c r="M2" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N2" s="4" t="inlineStr"/>
+      <c r="O2" s="4" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>refrigerant</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Refrigerant</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr"/>
+      <c r="F3" s="4" t="inlineStr"/>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr"/>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr"/>
+      <c r="K3" s="4" t="inlineStr"/>
+      <c r="L3" s="4" t="inlineStr"/>
+      <c r="M3" s="4" t="inlineStr"/>
+      <c r="N3" s="4" t="inlineStr"/>
+      <c r="O3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>bas_cntrl_manuf.</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>BAS Controller Manuf.</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr"/>
+      <c r="F4" s="4" t="inlineStr"/>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="inlineStr"/>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr"/>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr"/>
+      <c r="M4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N4" s="4" t="inlineStr"/>
+      <c r="O4" s="4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>condenser_type</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>See technology specific display names</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr"/>
+      <c r="F5" s="4" t="inlineStr"/>
+      <c r="G5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>Gas Cooler Type; user</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>Condenser Type; user</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr"/>
+      <c r="L5" s="4" t="inlineStr"/>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr">
+        <is>
+          <t>tech-label ✓; user/ref-by-tech: NOT impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>system_type</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>System Type</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>technology specific</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr"/>
+      <c r="F6" s="4" t="inlineStr"/>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>user/ref-by-tech: NOT impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>consultant</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Consultant</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>DCE</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr"/>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr"/>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr"/>
+      <c r="O7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>prepared_by</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Prepared By</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr"/>
+      <c r="F8" s="4" t="inlineStr"/>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr"/>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J8" s="4" t="inlineStr"/>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr"/>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr"/>
+      <c r="O8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>refrig_oem</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Refrig. OEM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr"/>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr"/>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr"/>
+      <c r="O9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>system_elec</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>System Elec.</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr"/>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr"/>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr"/>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr"/>
+      <c r="O10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>defrost_elec</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Defrost Elec.</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr"/>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr"/>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr"/>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr"/>
+      <c r="O11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>sys_pilot_elec</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Sys. Pilot Elec.</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr"/>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>208V 1 Ph</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr"/>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr"/>
+      <c r="K12" s="4" t="inlineStr"/>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr"/>
+      <c r="O12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>cond_elec</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>See technology specific display names</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>User</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr"/>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>460V 3 Ph 60Hz</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>Gas Cooler Elec</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>Condenser Elec</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr"/>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated; tech-label ✓; user/ref-by-tech: NOT impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>sg1_return_gas_temp</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SG1 Return Gas Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>technology specific</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr"/>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr"/>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr"/>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>user/ref-by-tech: NOT impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>sg2_return_gas_temp</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SG2 Return Gas Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>technology specific</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr"/>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr"/>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr"/>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>SG-gated; user/ref-by-tech: NOT impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>sg3_return_gas_temp</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SG3 Return Gas Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>technology specific</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr"/>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr"/>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr"/>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>SG-gated; user/ref-by-tech: NOT impl</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>design_db</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Design DB (�F)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr"/>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr"/>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr"/>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr"/>
+      <c r="O17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>design_wb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Design WB (�F)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr"/>
+      <c r="F18" s="4" t="inlineStr"/>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr"/>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr"/>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr"/>
+      <c r="O18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>design_interior_db</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Design Interior DB (�F)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>75�F</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr"/>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr"/>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr"/>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>SPEC: move to project information phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>design_interior_rh</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Design Interior RH (%)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr"/>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr"/>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr"/>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>SPEC: move to project information phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>sat_condensing_temp</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Sat. Condensing Dew Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr"/>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr"/>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr"/>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr"/>
+      <c r="O21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sat. Cond. Mid-Point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr"/>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr"/>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr"/>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr"/>
+      <c r="O22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Cond. Design TD Mid-Point (�F)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr"/>
+      <c r="F23" s="4" t="inlineStr"/>
+      <c r="G23" s="4" t="inlineStr"/>
+      <c r="H23" s="4" t="inlineStr"/>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr"/>
+      <c r="K23" s="4" t="inlineStr"/>
+      <c r="L23" s="4" t="inlineStr"/>
+      <c r="M23" s="4" t="inlineStr"/>
+      <c r="N23" s="4" t="inlineStr"/>
+      <c r="O23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>sg1_suct_temp</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SG1 Suct. Mid point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr"/>
+      <c r="F24" s="4" t="inlineStr"/>
+      <c r="G24" s="4" t="inlineStr"/>
+      <c r="H24" s="4" t="inlineStr"/>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr"/>
+      <c r="K24" s="4" t="inlineStr"/>
+      <c r="L24" s="4" t="inlineStr"/>
+      <c r="M24" s="4" t="inlineStr"/>
+      <c r="N24" s="4" t="inlineStr"/>
+      <c r="O24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>sg2_suct_temp</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SG2 Suct. Mid Point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr"/>
+      <c r="F25" s="4" t="inlineStr"/>
+      <c r="G25" s="4" t="inlineStr"/>
+      <c r="H25" s="4" t="inlineStr"/>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr"/>
+      <c r="K25" s="4" t="inlineStr"/>
+      <c r="L25" s="4" t="inlineStr"/>
+      <c r="M25" s="4" t="inlineStr"/>
+      <c r="N25" s="4" t="inlineStr"/>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>SG-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>sg3_suct_temp</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SG3 Suct. Mid-Point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr"/>
+      <c r="F26" s="4" t="inlineStr"/>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr"/>
+      <c r="I26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J26" s="4" t="inlineStr"/>
+      <c r="K26" s="4" t="inlineStr"/>
+      <c r="L26" s="4" t="inlineStr"/>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr"/>
+      <c r="O26" s="4" t="inlineStr">
+        <is>
+          <t>SG-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>See technology specific display names</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>SG1 Sat. Suct. Temp (�F)</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>SG1 Suct. Dew-Point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr"/>
+      <c r="L27" s="4" t="inlineStr"/>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr"/>
+      <c r="O27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>See technology specific display names</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>SG2 Sat. Suct. Temp (�F)</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>SG2 Suct. Dew-Point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr"/>
+      <c r="L28" s="4" t="inlineStr"/>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr"/>
+      <c r="O28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>See technology specific display names</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr"/>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>SG3 Sat. Suct. Temp (�F)</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>SG3 Suct. Dew-Point Temp (�F)</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr"/>
+      <c r="L29" s="4" t="inlineStr"/>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr"/>
+      <c r="O29" s="4" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>sg1_liquid_temp</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SG1 Liquid Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H30" s="4" t="inlineStr"/>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr"/>
+      <c r="O30" s="4" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>sg2_liquid_temp</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SG2 Liquid Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H31" s="4" t="inlineStr"/>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr"/>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>SG-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>sg3_liquid_temp</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SG3 Liquid Temp (�F)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr"/>
+      <c r="F32" s="4" t="inlineStr"/>
+      <c r="G32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H32" s="4" t="inlineStr"/>
+      <c r="I32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J32" s="4" t="inlineStr"/>
+      <c r="K32" s="4" t="inlineStr"/>
+      <c r="L32" s="4" t="inlineStr"/>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr"/>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>SG-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>num_suction_groups</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Num. Suction Groups</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr"/>
+      <c r="F33" s="4" t="inlineStr"/>
+      <c r="G33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H33" s="4" t="inlineStr"/>
+      <c r="I33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J33" s="4" t="inlineStr"/>
+      <c r="K33" s="4" t="inlineStr"/>
+      <c r="L33" s="4" t="inlineStr"/>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr"/>
+      <c r="O33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>See technology specific display names</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr"/>
+      <c r="F34" s="4" t="inlineStr"/>
+      <c r="G34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>Estimated Total System Refrigerant Charge (lbs)</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>Estimated Total System Refrigerant Charge (lbs)</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>Estimated Total System Refrigerant Charge (lbs)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>Estimated Total System Refrigerant Charge (Gal)</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Rack &amp; Cond. Charge� (lbs)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr"/>
+      <c r="F35" s="4" t="inlineStr"/>
+      <c r="G35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H35" s="4" t="inlineStr"/>
+      <c r="I35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J35" s="4" t="inlineStr"/>
+      <c r="K35" s="4" t="inlineStr"/>
+      <c r="L35" s="4" t="inlineStr"/>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr"/>
+      <c r="O35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Fixture and Field Piping (lbs)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr"/>
+      <c r="F36" s="4" t="inlineStr"/>
+      <c r="G36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H36" s="4" t="inlineStr"/>
+      <c r="I36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J36" s="4" t="inlineStr"/>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr"/>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr"/>
+      <c r="O36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Useful Superheat</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>technology specific</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr"/>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr"/>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr"/>
+      <c r="O37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Non-Useful Superheat</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>technology specific</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr"/>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr"/>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr"/>
+      <c r="O38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>5 yr. Extreme DB</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr"/>
+      <c r="E39" s="4" t="inlineStr"/>
+      <c r="F39" s="4" t="inlineStr"/>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr"/>
+      <c r="I39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J39" s="4" t="inlineStr"/>
+      <c r="K39" s="4" t="inlineStr"/>
+      <c r="L39" s="4" t="inlineStr"/>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr"/>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>SPEC: move to project information phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>50 yr. Exreme DB</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr"/>
+      <c r="E40" s="4" t="inlineStr"/>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr"/>
+      <c r="H40" s="4" t="inlineStr"/>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr"/>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr"/>
+      <c r="N40" s="4" t="inlineStr"/>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>SPEC: move to project information phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>0.4% Monthly Max WB</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr"/>
+      <c r="E41" s="4" t="inlineStr"/>
+      <c r="F41" s="4" t="inlineStr"/>
+      <c r="G41" s="4" t="inlineStr"/>
+      <c r="H41" s="4" t="inlineStr"/>
+      <c r="I41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J41" s="4" t="inlineStr"/>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr"/>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr"/>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>SPEC: move to project information phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Max 0.4% Monthly Design DB</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr"/>
+      <c r="E42" s="4" t="inlineStr"/>
+      <c r="F42" s="4" t="inlineStr"/>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr"/>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr"/>
+      <c r="K42" s="4" t="inlineStr"/>
+      <c r="L42" s="4" t="inlineStr"/>
+      <c r="M42" s="4" t="inlineStr"/>
+      <c r="N42" s="4" t="inlineStr"/>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>SPEC: move to project information phase</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Supply Fluid Temperature (�F)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr"/>
+      <c r="F43" s="4" t="inlineStr"/>
+      <c r="G43" s="4" t="inlineStr"/>
+      <c r="H43" s="4" t="inlineStr"/>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr"/>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr"/>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr"/>
+      <c r="O43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Return Fluid Temperature (�F)</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr"/>
+      <c r="F44" s="4" t="inlineStr"/>
+      <c r="G44" s="4" t="inlineStr"/>
+      <c r="H44" s="4" t="inlineStr"/>
+      <c r="I44" s="4" t="inlineStr"/>
+      <c r="J44" s="4" t="inlineStr"/>
+      <c r="K44" s="4" t="inlineStr"/>
+      <c r="L44" s="4" t="inlineStr"/>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr"/>
+      <c r="O44" s="4" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>secondary_refrigerant</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Secondary Refrigerant</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr"/>
+      <c r="F45" s="4" t="inlineStr"/>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr"/>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr"/>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr"/>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr"/>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>gas_cooler_leaving_temp</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Gas Cooler Leaving Refrig Temp (F)</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr"/>
+      <c r="F46" s="4" t="inlineStr"/>
+      <c r="G46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H46" s="4" t="inlineStr"/>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr"/>
+      <c r="K46" s="4" t="inlineStr"/>
+      <c r="L46" s="4" t="inlineStr"/>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr"/>
+      <c r="O46" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>flash_tank_sat_temp</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Flash Tank Sat. Temp (F)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr"/>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr"/>
+      <c r="N47" s="4" t="inlineStr"/>
+      <c r="O47" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>heat_reclaim_media</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Heat Reclaim Media</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H48" s="4" t="inlineStr"/>
+      <c r="I48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr"/>
+      <c r="O48" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>heat_reclaim_use</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Heat Reclaim Use</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Combo</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr"/>
+      <c r="F49" s="4" t="inlineStr"/>
+      <c r="G49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H49" s="4" t="inlineStr"/>
+      <c r="I49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J49" s="4" t="inlineStr"/>
+      <c r="K49" s="4" t="inlineStr"/>
+      <c r="L49" s="4" t="inlineStr"/>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr"/>
+      <c r="O49" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>est_summer_thr</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Est. Summer THR (MBH)</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr"/>
+      <c r="F50" s="4" t="inlineStr"/>
+      <c r="G50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H50" s="4" t="inlineStr"/>
+      <c r="I50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J50" s="4" t="inlineStr"/>
+      <c r="K50" s="4" t="inlineStr"/>
+      <c r="L50" s="4" t="inlineStr"/>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr"/>
+      <c r="O50" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>est_winter_thr</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Est. Winter THR (MBH)</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr"/>
+      <c r="F51" s="4" t="inlineStr"/>
+      <c r="G51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="H51" s="4" t="inlineStr"/>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr"/>
+      <c r="K51" s="4" t="inlineStr"/>
+      <c r="L51" s="4" t="inlineStr"/>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr"/>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>primary_refrig_liquid_temp</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Primary Refrig. Liquid Temp (F)</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr"/>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N52" s="4" t="inlineStr"/>
+      <c r="O52" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>primary_refrig_sst</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Primary Refrig. SST (F)</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr"/>
+      <c r="F53" s="4" t="inlineStr"/>
+      <c r="G53" s="4" t="inlineStr"/>
+      <c r="H53" s="4" t="inlineStr"/>
+      <c r="I53" s="4" t="inlineStr"/>
+      <c r="J53" s="4" t="inlineStr"/>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr"/>
+      <c r="M53" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N53" s="4" t="inlineStr"/>
+      <c r="O53" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>primary_refrig_hxr_superheat</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Primary Refrig. HXR Useful Superheat (F)</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr"/>
+      <c r="F54" s="4" t="inlineStr"/>
+      <c r="G54" s="4" t="inlineStr"/>
+      <c r="H54" s="4" t="inlineStr"/>
+      <c r="I54" s="4" t="inlineStr"/>
+      <c r="J54" s="4" t="inlineStr"/>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr"/>
+      <c r="M54" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N54" s="4" t="inlineStr"/>
+      <c r="O54" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>primary_refrig_sat_cond_temp</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Primary Refrig. Sat. Cond. Temp (F)</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D55" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E55" s="4" t="inlineStr"/>
+      <c r="F55" s="4" t="inlineStr"/>
+      <c r="G55" s="4" t="inlineStr"/>
+      <c r="H55" s="4" t="inlineStr"/>
+      <c r="I55" s="4" t="inlineStr"/>
+      <c r="J55" s="4" t="inlineStr"/>
+      <c r="K55" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L55" s="4" t="inlineStr"/>
+      <c r="M55" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N55" s="4" t="inlineStr"/>
+      <c r="O55" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>primary_refrig_return_gas_temp</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Primary Refrig. Return Gas Temp (F)</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr"/>
+      <c r="F56" s="4" t="inlineStr"/>
+      <c r="G56" s="4" t="inlineStr"/>
+      <c r="H56" s="4" t="inlineStr"/>
+      <c r="I56" s="4" t="inlineStr"/>
+      <c r="J56" s="4" t="inlineStr"/>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr"/>
+      <c r="M56" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N56" s="4" t="inlineStr"/>
+      <c r="O56" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>pump_skid_model</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Pump Skid Model</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D57" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr"/>
+      <c r="F57" s="4" t="inlineStr"/>
+      <c r="G57" s="4" t="inlineStr"/>
+      <c r="H57" s="4" t="inlineStr"/>
+      <c r="I57" s="4" t="inlineStr"/>
+      <c r="J57" s="4" t="inlineStr"/>
+      <c r="K57" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L57" s="4" t="inlineStr"/>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr"/>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>pump_skid_min_capacity_gpm</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Pump Skid Minimum Capacity (GPM)</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>pump_skid_max_capacity_gpm</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Pump Skid Maximum Capacity (GPM)</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D59" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E59" s="4" t="inlineStr"/>
+      <c r="F59" s="4" t="inlineStr"/>
+      <c r="G59" s="4" t="inlineStr"/>
+      <c r="H59" s="4" t="inlineStr"/>
+      <c r="I59" s="4" t="inlineStr"/>
+      <c r="J59" s="4" t="inlineStr"/>
+      <c r="K59" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L59" s="4" t="inlineStr"/>
+      <c r="M59" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N59" s="4" t="inlineStr"/>
+      <c r="O59" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>pump_skid_hxr_approach</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Pump Skid HXR Approach (F)</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D60" s="4" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="E60" s="4" t="inlineStr"/>
+      <c r="F60" s="4" t="inlineStr"/>
+      <c r="G60" s="4" t="inlineStr"/>
+      <c r="H60" s="4" t="inlineStr"/>
+      <c r="I60" s="4" t="inlineStr"/>
+      <c r="J60" s="4" t="inlineStr"/>
+      <c r="K60" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L60" s="4" t="inlineStr"/>
+      <c r="M60" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="N60" s="4" t="inlineStr"/>
+      <c r="O60" s="4" t="inlineStr">
+        <is>
+          <t>refrigerant-gated</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:O1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AA52"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="9" customWidth="1" min="13" max="13"/>
+    <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
+    <col width="9" customWidth="1" min="16" max="16"/>
+    <col width="9" customWidth="1" min="17" max="17"/>
+    <col width="9" customWidth="1" min="18" max="18"/>
+    <col width="9" customWidth="1" min="19" max="19"/>
+    <col width="9" customWidth="1" min="20" max="20"/>
+    <col width="9" customWidth="1" min="21" max="21"/>
+    <col width="9" customWidth="1" min="22" max="22"/>
+    <col width="9" customWidth="1" min="23" max="23"/>
+    <col width="9" customWidth="1" min="24" max="24"/>
+    <col width="9" customWidth="1" min="25" max="25"/>
+    <col width="9" customWidth="1" min="26" max="26"/>
+    <col width="9" customWidth="1" min="27" max="27"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2</t>
+        </is>
+      </c>
+      <c r="E1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2</t>
+        </is>
+      </c>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2</t>
+        </is>
+      </c>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>TCO2</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="inlineStr">
+        <is>
+          <t>HFC DX</t>
+        </is>
+      </c>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>HFC DX</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="inlineStr">
+        <is>
+          <t>HFC DX</t>
+        </is>
+      </c>
+      <c r="M1" s="3" t="inlineStr">
+        <is>
+          <t>HFC DX</t>
+        </is>
+      </c>
+      <c r="N1" s="3" t="inlineStr">
+        <is>
+          <t>HFC DX</t>
+        </is>
+      </c>
+      <c r="O1" s="3" t="inlineStr">
+        <is>
+          <t>HFC DX</t>
+        </is>
+      </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2</t>
+        </is>
+      </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2</t>
+        </is>
+      </c>
+      <c r="R1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2</t>
+        </is>
+      </c>
+      <c r="S1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2</t>
+        </is>
+      </c>
+      <c r="T1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2</t>
+        </is>
+      </c>
+      <c r="U1" s="3" t="inlineStr">
+        <is>
+          <t>SCO2</t>
+        </is>
+      </c>
+      <c r="V1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol</t>
+        </is>
+      </c>
+      <c r="W1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol</t>
+        </is>
+      </c>
+      <c r="X1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol</t>
+        </is>
+      </c>
+      <c r="Y1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol</t>
+        </is>
+      </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t>Glycol</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr"/>
+      <c r="B2" s="5" t="inlineStr"/>
+      <c r="C2" s="5" t="inlineStr"/>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>Case(DB)</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="inlineStr">
+        <is>
+          <t>Case(Man)</t>
+        </is>
+      </c>
+      <c r="F2" s="5" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
+        </is>
+      </c>
+      <c r="G2" s="5" t="inlineStr">
+        <is>
+          <t>Skid</t>
+        </is>
+      </c>
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="I2" s="5" t="inlineStr">
+        <is>
+          <t>Stub</t>
+        </is>
+      </c>
+      <c r="J2" s="5" t="inlineStr">
+        <is>
+          <t>Case(DB)</t>
+        </is>
+      </c>
+      <c r="K2" s="5" t="inlineStr">
+        <is>
+          <t>Case(Man)</t>
+        </is>
+      </c>
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
+        </is>
+      </c>
+      <c r="M2" s="5" t="inlineStr">
+        <is>
+          <t>Skid</t>
+        </is>
+      </c>
+      <c r="N2" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="O2" s="5" t="inlineStr">
+        <is>
+          <t>Stub</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="inlineStr">
+        <is>
+          <t>Case(DB)</t>
+        </is>
+      </c>
+      <c r="Q2" s="5" t="inlineStr">
+        <is>
+          <t>Case(Man)</t>
+        </is>
+      </c>
+      <c r="R2" s="5" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
+        </is>
+      </c>
+      <c r="S2" s="5" t="inlineStr">
+        <is>
+          <t>Skid</t>
+        </is>
+      </c>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>Stub</t>
+        </is>
+      </c>
+      <c r="V2" s="5" t="inlineStr">
+        <is>
+          <t>Case(DB)</t>
+        </is>
+      </c>
+      <c r="W2" s="5" t="inlineStr">
+        <is>
+          <t>Case(Man)</t>
+        </is>
+      </c>
+      <c r="X2" s="5" t="inlineStr">
+        <is>
+          <t>Walk-in</t>
+        </is>
+      </c>
+      <c r="Y2" s="5" t="inlineStr">
+        <is>
+          <t>Skid</t>
+        </is>
+      </c>
+      <c r="Z2" s="5" t="inlineStr">
+        <is>
+          <t>Custom</t>
+        </is>
+      </c>
+      <c r="AA2" s="5" t="inlineStr">
+        <is>
+          <t>Stub</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>circuit_name</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y3" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA3" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>circuit_type</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Type</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr"/>
+      <c r="H4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M4" s="4" t="inlineStr"/>
+      <c r="N4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y4" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA4" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>mode</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Mode</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G5" s="4" t="inlineStr"/>
+      <c r="H5" s="4" t="inlineStr"/>
+      <c r="I5" s="4" t="inlineStr"/>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr"/>
+      <c r="N5" s="4" t="inlineStr"/>
+      <c r="O5" s="4" t="inlineStr"/>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr"/>
+      <c r="U5" s="4" t="inlineStr"/>
+      <c r="V5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="inlineStr"/>
+      <c r="AA5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Model</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G6" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr"/>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr"/>
+      <c r="P6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr"/>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y6" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA6" s="4" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>evap_hx_qty</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Evap./Hx Qty</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr"/>
+      <c r="E7" s="4" t="inlineStr"/>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="inlineStr"/>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr"/>
+      <c r="J7" s="4" t="inlineStr"/>
+      <c r="K7" s="4" t="inlineStr"/>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr"/>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr"/>
+      <c r="P7" s="4" t="inlineStr"/>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr"/>
+      <c r="V7" s="4" t="inlineStr"/>
+      <c r="W7" s="4" t="inlineStr"/>
+      <c r="X7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>manufacturer</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Manuf.</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr"/>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr"/>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr"/>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>length_unit</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>ft/drs</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr"/>
+      <c r="G9" s="4" t="inlineStr"/>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr"/>
+      <c r="M9" s="4" t="inlineStr"/>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr"/>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="inlineStr"/>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr"/>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="inlineStr"/>
+      <c r="Y9" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>total_length</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr"/>
+      <c r="G10" s="4" t="inlineStr"/>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr"/>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr"/>
+      <c r="M10" s="4" t="inlineStr"/>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr"/>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="inlineStr"/>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr"/>
+      <c r="V10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="inlineStr"/>
+      <c r="Y10" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA10" s="4" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>qty_2drs_4ft</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2drs/4'</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr"/>
+      <c r="G11" s="4" t="inlineStr"/>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr"/>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr"/>
+      <c r="M11" s="4" t="inlineStr"/>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr"/>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="inlineStr"/>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="inlineStr"/>
+      <c r="Y11" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA11" s="4" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>qty_3drs_6ft</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>3drs/6'</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr"/>
+      <c r="G12" s="4" t="inlineStr"/>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr"/>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr"/>
+      <c r="M12" s="4" t="inlineStr"/>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr"/>
+      <c r="P12" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="inlineStr"/>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr"/>
+      <c r="V12" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="W12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="inlineStr"/>
+      <c r="Y12" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>qty_4drs_8ft</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>4drs/8'</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr"/>
+      <c r="G13" s="4" t="inlineStr"/>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr"/>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O13" s="4" t="inlineStr"/>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="inlineStr"/>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr"/>
+      <c r="V13" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="inlineStr"/>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA13" s="4" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>qty_5drs_12ft</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>5drs/12'</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr"/>
+      <c r="G14" s="4" t="inlineStr"/>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr"/>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr"/>
+      <c r="M14" s="4" t="inlineStr"/>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr"/>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="Q14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="inlineStr"/>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr"/>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="W14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="inlineStr"/>
+      <c r="Y14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA14" s="4" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>walk_in_length</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr"/>
+      <c r="E15" s="4" t="inlineStr"/>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr"/>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr"/>
+      <c r="J15" s="4" t="inlineStr"/>
+      <c r="K15" s="4" t="inlineStr"/>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr"/>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr"/>
+      <c r="P15" s="4" t="inlineStr"/>
+      <c r="Q15" s="4" t="inlineStr"/>
+      <c r="R15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr"/>
+      <c r="V15" s="4" t="inlineStr"/>
+      <c r="W15" s="4" t="inlineStr"/>
+      <c r="X15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>walk_in_width</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr"/>
+      <c r="E16" s="4" t="inlineStr"/>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr"/>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr"/>
+      <c r="J16" s="4" t="inlineStr"/>
+      <c r="K16" s="4" t="inlineStr"/>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr"/>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr"/>
+      <c r="P16" s="4" t="inlineStr"/>
+      <c r="Q16" s="4" t="inlineStr"/>
+      <c r="R16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr"/>
+      <c r="V16" s="4" t="inlineStr"/>
+      <c r="W16" s="4" t="inlineStr"/>
+      <c r="X16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>walk_in_height</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr"/>
+      <c r="E17" s="4" t="inlineStr"/>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr"/>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr"/>
+      <c r="J17" s="4" t="inlineStr"/>
+      <c r="K17" s="4" t="inlineStr"/>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr"/>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr"/>
+      <c r="P17" s="4" t="inlineStr"/>
+      <c r="Q17" s="4" t="inlineStr"/>
+      <c r="R17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr"/>
+      <c r="V17" s="4" t="inlineStr"/>
+      <c r="W17" s="4" t="inlineStr"/>
+      <c r="X17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y17" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>application</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Application</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="Q18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="W18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA18" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>lshx</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>LSHX</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>checkbox</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr"/>
+      <c r="E19" s="4" t="inlineStr"/>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr"/>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr"/>
+      <c r="J19" s="4" t="inlineStr"/>
+      <c r="K19" s="4" t="inlineStr"/>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr"/>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr"/>
+      <c r="P19" s="4" t="inlineStr"/>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr"/>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr"/>
+      <c r="V19" s="4" t="inlineStr"/>
+      <c r="W19" s="4" t="inlineStr"/>
+      <c r="X19" s="4" t="inlineStr"/>
+      <c r="Y19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA19" s="4" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>heat_exchanger_model</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Heat Exch. Model</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr"/>
+      <c r="E20" s="4" t="inlineStr"/>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr"/>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr"/>
+      <c r="J20" s="4" t="inlineStr"/>
+      <c r="K20" s="4" t="inlineStr"/>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr"/>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr"/>
+      <c r="P20" s="4" t="inlineStr"/>
+      <c r="Q20" s="4" t="inlineStr"/>
+      <c r="R20" s="4" t="inlineStr"/>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr"/>
+      <c r="V20" s="4" t="inlineStr"/>
+      <c r="W20" s="4" t="inlineStr"/>
+      <c r="X20" s="4" t="inlineStr"/>
+      <c r="Y20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA20" s="4" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>expansion_valve</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Expan. Valve</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr"/>
+      <c r="E21" s="4" t="inlineStr"/>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr"/>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr"/>
+      <c r="J21" s="4" t="inlineStr"/>
+      <c r="K21" s="4" t="inlineStr"/>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr"/>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O21" s="4" t="inlineStr"/>
+      <c r="P21" s="4" t="inlineStr"/>
+      <c r="Q21" s="4" t="inlineStr"/>
+      <c r="R21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr"/>
+      <c r="V21" s="4" t="inlineStr"/>
+      <c r="W21" s="4" t="inlineStr"/>
+      <c r="X21" s="4" t="inlineStr"/>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA21" s="4" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>distributer_nozzle</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Distr. Nozzle</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr"/>
+      <c r="E22" s="4" t="inlineStr"/>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr"/>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr"/>
+      <c r="J22" s="4" t="inlineStr"/>
+      <c r="K22" s="4" t="inlineStr"/>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr"/>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr"/>
+      <c r="P22" s="4" t="inlineStr"/>
+      <c r="Q22" s="4" t="inlineStr"/>
+      <c r="R22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr"/>
+      <c r="V22" s="4" t="inlineStr"/>
+      <c r="W22" s="4" t="inlineStr"/>
+      <c r="X22" s="4" t="inlineStr"/>
+      <c r="Y22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA22" s="4" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>circuit_load</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Circuit Load (MBH)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr"/>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr"/>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr"/>
+      <c r="V23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA23" s="4" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>evap_temp</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Evap. Temp.</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr"/>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr"/>
+      <c r="P24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr"/>
+      <c r="V24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>suct_temp</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Suct. Temp.</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr"/>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr"/>
+      <c r="P25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr"/>
+      <c r="V25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y25" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z25" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA25" s="4" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>case_room_temp</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Case/Room Temp.</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr"/>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I26" s="4" t="inlineStr"/>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr"/>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O26" s="4" t="inlineStr"/>
+      <c r="P26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr"/>
+      <c r="V26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y26" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA26" s="4" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>evap_pres_reg</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>EPR</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr"/>
+      <c r="E27" s="4" t="inlineStr"/>
+      <c r="F27" s="4" t="inlineStr"/>
+      <c r="G27" s="4" t="inlineStr"/>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr"/>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr"/>
+      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="R27" s="4" t="inlineStr"/>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr"/>
+      <c r="W27" s="4" t="inlineStr"/>
+      <c r="X27" s="4" t="inlineStr"/>
+      <c r="Y27" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA27" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>suct_valve_delta</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Suct. Valve ?P</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr"/>
+      <c r="E28" s="4" t="inlineStr"/>
+      <c r="F28" s="4" t="inlineStr"/>
+      <c r="G28" s="4" t="inlineStr"/>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr"/>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr"/>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr"/>
+      <c r="P28" s="4" t="inlineStr"/>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr"/>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr"/>
+      <c r="V28" s="4" t="inlineStr"/>
+      <c r="W28" s="4" t="inlineStr"/>
+      <c r="X28" s="4" t="inlineStr"/>
+      <c r="Y28" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z28" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA28" s="4" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>liq_line_sol_valve</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>LLSV</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr"/>
+      <c r="E29" s="4" t="inlineStr"/>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr"/>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr"/>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr"/>
+      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="inlineStr"/>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr"/>
+      <c r="W29" s="4" t="inlineStr"/>
+      <c r="X29" s="4" t="inlineStr"/>
+      <c r="Y29" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA29" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>auto_flow_balance_valve</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ABV</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr"/>
+      <c r="E30" s="4" t="inlineStr"/>
+      <c r="F30" s="4" t="inlineStr"/>
+      <c r="G30" s="4" t="inlineStr"/>
+      <c r="H30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J30" s="4" t="inlineStr"/>
+      <c r="K30" s="4" t="inlineStr"/>
+      <c r="L30" s="4" t="inlineStr"/>
+      <c r="M30" s="4" t="inlineStr"/>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr"/>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr"/>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr"/>
+      <c r="W30" s="4" t="inlineStr"/>
+      <c r="X30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y30" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA30" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>supply_line_soneloid_valve</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SLSV</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr"/>
+      <c r="E31" s="4" t="inlineStr"/>
+      <c r="F31" s="4" t="inlineStr"/>
+      <c r="G31" s="4" t="inlineStr"/>
+      <c r="H31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J31" s="4" t="inlineStr"/>
+      <c r="K31" s="4" t="inlineStr"/>
+      <c r="L31" s="4" t="inlineStr"/>
+      <c r="M31" s="4" t="inlineStr"/>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr"/>
+      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr"/>
+      <c r="W31" s="4" t="inlineStr"/>
+      <c r="X31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y31" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA31" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>defrost_type</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Defrost Type</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="inlineStr"/>
+      <c r="H32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I32" s="4" t="inlineStr"/>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr"/>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr"/>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr"/>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y32" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA32" s="4" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>defrost_amps</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Defrost Amps</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="inlineStr"/>
+      <c r="H33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I33" s="4" t="inlineStr"/>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr"/>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr"/>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr"/>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y33" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z33" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA33" s="4" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>defrost_volts</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Defrost Volts</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="inlineStr"/>
+      <c r="H34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I34" s="4" t="inlineStr"/>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="K34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr"/>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr"/>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr"/>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y34" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z34" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA34" s="4" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>fan_amps</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Fan Amps</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="inlineStr"/>
+      <c r="H35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I35" s="4" t="inlineStr"/>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr"/>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr"/>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y35" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA35" s="4" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>fan_volts</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Fan Volts</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="inlineStr"/>
+      <c r="H36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I36" s="4" t="inlineStr"/>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr"/>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr"/>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr"/>
+      <c r="V36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y36" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z36" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA36" s="4" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>lights</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Lights</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="inlineStr"/>
+      <c r="G37" s="4" t="inlineStr"/>
+      <c r="H37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I37" s="4" t="inlineStr"/>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr"/>
+      <c r="M37" s="4" t="inlineStr"/>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr"/>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="inlineStr"/>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr"/>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X37" s="4" t="inlineStr"/>
+      <c r="Y37" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z37" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA37" s="4" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>anti_sweat</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Anti-Sweat</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="inlineStr"/>
+      <c r="G38" s="4" t="inlineStr"/>
+      <c r="H38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I38" s="4" t="inlineStr"/>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr"/>
+      <c r="M38" s="4" t="inlineStr"/>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr"/>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="inlineStr"/>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr"/>
+      <c r="V38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="inlineStr"/>
+      <c r="Y38" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z38" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA38" s="4" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>refrig_charge</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Refrig. Charge</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="inlineStr"/>
+      <c r="H39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I39" s="4" t="inlineStr"/>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr"/>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr"/>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr"/>
+      <c r="V39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y39" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z39" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA39" s="4" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>wm_equip_tag</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>WM Equip. Tag</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="inlineStr"/>
+      <c r="G40" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I40" s="4" t="inlineStr"/>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr"/>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr"/>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="inlineStr"/>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr"/>
+      <c r="V40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X40" s="4" t="inlineStr"/>
+      <c r="Y40" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z40" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA40" s="4" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>num_sub_ckts</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t># Sub-CKTs</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="H41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I41" s="4" t="inlineStr"/>
+      <c r="J41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr"/>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr"/>
+      <c r="V41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y41" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z41" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA41" s="4" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>main_circuit</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Main Circuit</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I42" s="4" t="inlineStr"/>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr"/>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr"/>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y42" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z42" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA42" s="4" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>sub_circuit_load</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Sub-Circuit Load (MBH)</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr"/>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr"/>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr"/>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y43" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z43" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA43" s="4" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>suction_group</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Suction Group</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>combo</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="H44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>user</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y44" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA44" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>location</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Location of valves</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="inlineStr"/>
+      <c r="H45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I45" s="4" t="inlineStr"/>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr"/>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr"/>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr"/>
+      <c r="V45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y45" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z45" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA45" s="4" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>const_phase</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Construction Phase Sequence</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="inlineStr"/>
+      <c r="H46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I46" s="4" t="inlineStr"/>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M46" s="4" t="inlineStr"/>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O46" s="4" t="inlineStr"/>
+      <c r="P46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr"/>
+      <c r="V46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y46" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z46" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA46" s="4" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Flow (GPM)</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr"/>
+      <c r="E47" s="4" t="inlineStr"/>
+      <c r="F47" s="4" t="inlineStr"/>
+      <c r="G47" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="H47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I47" s="4" t="inlineStr"/>
+      <c r="J47" s="4" t="inlineStr"/>
+      <c r="K47" s="4" t="inlineStr"/>
+      <c r="L47" s="4" t="inlineStr"/>
+      <c r="M47" s="4" t="inlineStr">
+        <is>
+          <t>ref</t>
+        </is>
+      </c>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O47" s="4" t="inlineStr"/>
+      <c r="P47" s="4" t="inlineStr"/>
+      <c r="Q47" s="4" t="inlineStr"/>
+      <c r="R47" s="4" t="inlineStr"/>
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="inlineStr"/>
+      <c r="V47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X47" s="4" t="inlineStr"/>
+      <c r="Y47" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z47" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA47" s="4" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>circulation_rate</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Circulation Rate</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D48" s="4" t="inlineStr"/>
+      <c r="E48" s="4" t="inlineStr"/>
+      <c r="F48" s="4" t="inlineStr"/>
+      <c r="G48" s="4" t="inlineStr"/>
+      <c r="H48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I48" s="4" t="inlineStr"/>
+      <c r="J48" s="4" t="inlineStr"/>
+      <c r="K48" s="4" t="inlineStr"/>
+      <c r="L48" s="4" t="inlineStr"/>
+      <c r="M48" s="4" t="inlineStr"/>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O48" s="4" t="inlineStr"/>
+      <c r="P48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="inlineStr"/>
+      <c r="V48" s="4" t="inlineStr"/>
+      <c r="W48" s="4" t="inlineStr"/>
+      <c r="X48" s="4" t="inlineStr"/>
+      <c r="Y48" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z48" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA48" s="4" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>comments</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="inlineStr"/>
+      <c r="H49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I49" s="4" t="inlineStr"/>
+      <c r="J49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M49" s="4" t="inlineStr"/>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O49" s="4" t="inlineStr"/>
+      <c r="P49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U49" s="4" t="inlineStr"/>
+      <c r="V49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y49" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z49" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA49" s="4" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>equip_number</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Equip Number</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="inlineStr"/>
+      <c r="H50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I50" s="4" t="inlineStr"/>
+      <c r="J50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M50" s="4" t="inlineStr"/>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O50" s="4" t="inlineStr"/>
+      <c r="P50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr"/>
+      <c r="V50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y50" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z50" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA50" s="4" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>notes</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="inlineStr"/>
+      <c r="H51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="J51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="M51" s="4" t="inlineStr"/>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="P51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="V51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y51" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA51" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>fixture_delta_p</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Fixture ?P</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr"/>
+      <c r="E52" s="4" t="inlineStr"/>
+      <c r="F52" s="4" t="inlineStr"/>
+      <c r="G52" s="4" t="inlineStr"/>
+      <c r="H52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="I52" s="4" t="inlineStr"/>
+      <c r="J52" s="4" t="inlineStr"/>
+      <c r="K52" s="4" t="inlineStr"/>
+      <c r="L52" s="4" t="inlineStr"/>
+      <c r="M52" s="4" t="inlineStr"/>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="O52" s="4" t="inlineStr"/>
+      <c r="P52" s="4" t="inlineStr"/>
+      <c r="Q52" s="4" t="inlineStr"/>
+      <c r="R52" s="4" t="inlineStr"/>
+      <c r="S52" s="4" t="inlineStr"/>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr"/>
+      <c r="V52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="W52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="X52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="Y52" s="4" t="inlineStr"/>
+      <c r="Z52" s="4" t="inlineStr">
+        <is>
+          <t>y</t>
+        </is>
+      </c>
+      <c r="AA52" s="4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:AA1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="80" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="3" t="inlineStr">
+        <is>
+          <t>Gap</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="inlineStr">
+        <is>
+          <t>Detail</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Coverage</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>All ~93 REV1 fields exist in impl</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="D2" s="4" t="inlineStr">
+        <is>
+          <t>Only diff: spec typo 'supply_line_soneloid_valve' vs impl 'supply_line_solenoid_valve'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>#4 Hide vs disable</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Non-applicable fields must HIDE, not grey</t>
+        </is>
+      </c>
+      <c r="C3" s="6" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>System Info now hides fields whose rule is Enabled=0 (SG2/SG3 when num_suction_groups=1; DX fields under Glycol/CO2). Verified at model level.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>#2 User/Reference by tech</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Field is user-input for one tech, reference for another</t>
+        </is>
+      </c>
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D4" s="4" t="inlineStr">
+        <is>
+          <t>_TECH_REFERENCE map is EMPTY. e.g. sg{n}_return_gas_temp ref@TCO2/user@HFC; system_type user@TCO2,HFC / ref@SCO2,Glycol — not enforced.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>#1/#3 Per-tech applicability + display names</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Full REV1 tech matrix + tech labels</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>PARTIAL</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>_TECH_LABELS covers 5 fields (condenser_type, cond_elec, sg{n}_sat_suct_temp, est_total_refrig_charge). Some refrigerant gating exists; full matrix not encoded.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>#5 Move to Project Info</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>design_interior_db, design_interior_rh</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>GAP</t>
+        </is>
+      </c>
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>Spec marks them 'move to project information phase'; still in System Info.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>